--- a/output/roomself_excel/14593.xlsx
+++ b/output/roomself_excel/14593.xlsx
@@ -466,20 +466,20 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Kitchen</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>485065</v>
+        <v>173442</v>
       </c>
       <c r="D2" t="n">
-        <v>6536</v>
+        <v>3436</v>
       </c>
       <c r="E2" t="n">
-        <v>954</v>
+        <v>239</v>
       </c>
       <c r="F2" t="n">
-        <v>583</v>
+        <v>49</v>
       </c>
     </row>
     <row r="3">
@@ -510,20 +510,20 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Living Room</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>6319</v>
+        <v>364672</v>
       </c>
       <c r="D4" t="n">
-        <v>640</v>
+        <v>5048</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>443</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
     </row>
     <row r="5">
@@ -532,20 +532,20 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>6003</v>
+        <v>105589</v>
       </c>
       <c r="D5" t="n">
-        <v>624</v>
+        <v>2600</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>380</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>344</v>
       </c>
     </row>
     <row r="6">
@@ -554,20 +554,20 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Hallway</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>155533</v>
+        <v>208754</v>
       </c>
       <c r="D6" t="n">
-        <v>4032</v>
+        <v>3660</v>
       </c>
       <c r="E6" t="n">
-        <v>426</v>
+        <v>434</v>
       </c>
       <c r="F6" t="n">
-        <v>294</v>
+        <v>45</v>
       </c>
     </row>
     <row r="7">
@@ -576,20 +576,20 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>16633</v>
+        <v>116935</v>
       </c>
       <c r="D7" t="n">
-        <v>1128</v>
+        <v>2848</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>257</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
     </row>
     <row r="8">
@@ -620,20 +620,20 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Living Room</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>364672</v>
+        <v>76954</v>
       </c>
       <c r="D9" t="n">
-        <v>5048</v>
+        <v>2284</v>
       </c>
       <c r="E9" t="n">
-        <v>443</v>
+        <v>397</v>
       </c>
       <c r="F9" t="n">
-        <v>45</v>
+        <v>185</v>
       </c>
     </row>
     <row r="10">
@@ -642,20 +642,20 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>21823</v>
+        <v>155533</v>
       </c>
       <c r="D10" t="n">
-        <v>1184</v>
+        <v>4032</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>426</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>294</v>
       </c>
     </row>
     <row r="11">
@@ -664,14 +664,14 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>42500</v>
+        <v>19097</v>
       </c>
       <c r="D11" t="n">
-        <v>1680</v>
+        <v>1128</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -690,10 +690,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>19097</v>
+        <v>25454</v>
       </c>
       <c r="D12" t="n">
-        <v>1128</v>
+        <v>1380</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -708,20 +708,20 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>173442</v>
+        <v>485065</v>
       </c>
       <c r="D13" t="n">
-        <v>3436</v>
+        <v>6536</v>
       </c>
       <c r="E13" t="n">
-        <v>247</v>
+        <v>954</v>
       </c>
       <c r="F13" t="n">
-        <v>234</v>
+        <v>583</v>
       </c>
     </row>
     <row r="14">
@@ -730,20 +730,20 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>105589</v>
+        <v>6319</v>
       </c>
       <c r="D14" t="n">
-        <v>2600</v>
+        <v>640</v>
       </c>
       <c r="E14" t="n">
-        <v>380</v>
+        <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>344</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -756,16 +756,16 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>116191</v>
+        <v>6003</v>
       </c>
       <c r="D15" t="n">
-        <v>4000</v>
+        <v>624</v>
       </c>
       <c r="E15" t="n">
-        <v>151</v>
+        <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -774,14 +774,14 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>25454</v>
+        <v>16633</v>
       </c>
       <c r="D16" t="n">
-        <v>1380</v>
+        <v>1128</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -796,20 +796,20 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>208754</v>
+        <v>21823</v>
       </c>
       <c r="D17" t="n">
-        <v>3660</v>
+        <v>1184</v>
       </c>
       <c r="E17" t="n">
-        <v>434</v>
+        <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>11886</v>
+        <v>42500</v>
       </c>
       <c r="D18" t="n">
-        <v>908</v>
+        <v>1680</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -840,20 +840,20 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>76954</v>
+        <v>116191</v>
       </c>
       <c r="D19" t="n">
-        <v>2284</v>
+        <v>4000</v>
       </c>
       <c r="E19" t="n">
-        <v>397</v>
+        <v>151</v>
       </c>
       <c r="F19" t="n">
-        <v>185</v>
+        <v>65</v>
       </c>
     </row>
     <row r="20">
@@ -866,16 +866,16 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>22657</v>
+        <v>11886</v>
       </c>
       <c r="D20" t="n">
-        <v>1208</v>
+        <v>908</v>
       </c>
       <c r="E20" t="n">
-        <v>163</v>
+        <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -884,20 +884,20 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>116935</v>
+        <v>22657</v>
       </c>
       <c r="D21" t="n">
-        <v>2848</v>
+        <v>1208</v>
       </c>
       <c r="E21" t="n">
-        <v>696</v>
+        <v>163</v>
       </c>
       <c r="F21" t="n">
-        <v>257</v>
+        <v>44</v>
       </c>
     </row>
     <row r="22">

--- a/output/roomself_excel/14593.xlsx
+++ b/output/roomself_excel/14593.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F22"/>
+  <dimension ref="A1:P22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,12 +451,62 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallLength</t>
+          <t>WallDir_1</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallWidth</t>
+          <t>ExtWallLength_1</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_1</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_2</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_2</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_2</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_3</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_3</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_3</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_4</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_4</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_4</t>
         </is>
       </c>
     </row>
@@ -475,12 +525,26 @@
       <c r="D2" t="n">
         <v>3436</v>
       </c>
-      <c r="E2" t="n">
-        <v>239</v>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F2" t="n">
+        <v>227</v>
+      </c>
+      <c r="G2" t="n">
         <v>49</v>
       </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -497,11 +561,49 @@
       <c r="D3" t="n">
         <v>4496</v>
       </c>
-      <c r="E3" t="n">
-        <v>628</v>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F3" t="n">
-        <v>170</v>
+        <v>458</v>
+      </c>
+      <c r="G3" t="n">
+        <v>45</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>63</v>
+      </c>
+      <c r="J3" t="n">
+        <v>63</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
+        <v>62</v>
+      </c>
+      <c r="M3" t="n">
+        <v>61</v>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="O3" t="n">
+        <v>414</v>
+      </c>
+      <c r="P3" t="n">
+        <v>44</v>
       </c>
     </row>
     <row r="4">
@@ -519,12 +621,26 @@
       <c r="D4" t="n">
         <v>5048</v>
       </c>
-      <c r="E4" t="n">
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
         <v>443</v>
       </c>
-      <c r="F4" t="n">
+      <c r="G4" t="n">
         <v>45</v>
       </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -541,12 +657,34 @@
       <c r="D5" t="n">
         <v>2600</v>
       </c>
-      <c r="E5" t="n">
-        <v>380</v>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F5" t="n">
-        <v>344</v>
-      </c>
+        <v>331</v>
+      </c>
+      <c r="G5" t="n">
+        <v>25</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>319</v>
+      </c>
+      <c r="J5" t="n">
+        <v>49</v>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -563,12 +701,26 @@
       <c r="D6" t="n">
         <v>3660</v>
       </c>
-      <c r="E6" t="n">
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
         <v>434</v>
       </c>
-      <c r="F6" t="n">
+      <c r="G6" t="n">
         <v>45</v>
       </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -585,12 +737,34 @@
       <c r="D7" t="n">
         <v>2848</v>
       </c>
-      <c r="E7" t="n">
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
         <v>257</v>
       </c>
-      <c r="F7" t="n">
+      <c r="G7" t="n">
         <v>45</v>
       </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>455</v>
+      </c>
+      <c r="J7" t="n">
+        <v>39</v>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -607,12 +781,18 @@
       <c r="D8" t="n">
         <v>2032</v>
       </c>
-      <c r="E8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0</v>
-      </c>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -629,12 +809,34 @@
       <c r="D9" t="n">
         <v>2284</v>
       </c>
-      <c r="E9" t="n">
-        <v>397</v>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F9" t="n">
-        <v>185</v>
-      </c>
+        <v>127</v>
+      </c>
+      <c r="G9" t="n">
+        <v>44</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>353</v>
+      </c>
+      <c r="J9" t="n">
+        <v>46</v>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -651,12 +853,34 @@
       <c r="D10" t="n">
         <v>4032</v>
       </c>
-      <c r="E10" t="n">
-        <v>426</v>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F10" t="n">
-        <v>294</v>
-      </c>
+        <v>269</v>
+      </c>
+      <c r="G10" t="n">
+        <v>39</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>354</v>
+      </c>
+      <c r="J10" t="n">
+        <v>25</v>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -673,12 +897,18 @@
       <c r="D11" t="n">
         <v>1128</v>
       </c>
-      <c r="E11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0</v>
-      </c>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -695,12 +925,18 @@
       <c r="D12" t="n">
         <v>1380</v>
       </c>
-      <c r="E12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" t="n">
-        <v>0</v>
-      </c>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -717,12 +953,34 @@
       <c r="D13" t="n">
         <v>6536</v>
       </c>
-      <c r="E13" t="n">
-        <v>954</v>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F13" t="n">
-        <v>583</v>
-      </c>
+        <v>933</v>
+      </c>
+      <c r="G13" t="n">
+        <v>45</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>538</v>
+      </c>
+      <c r="J13" t="n">
+        <v>21</v>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -739,12 +997,18 @@
       <c r="D14" t="n">
         <v>640</v>
       </c>
-      <c r="E14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0</v>
-      </c>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -761,12 +1025,18 @@
       <c r="D15" t="n">
         <v>624</v>
       </c>
-      <c r="E15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0</v>
-      </c>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -783,12 +1053,18 @@
       <c r="D16" t="n">
         <v>1128</v>
       </c>
-      <c r="E16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0</v>
-      </c>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -805,12 +1081,18 @@
       <c r="D17" t="n">
         <v>1184</v>
       </c>
-      <c r="E17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0</v>
-      </c>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -827,12 +1109,18 @@
       <c r="D18" t="n">
         <v>1680</v>
       </c>
-      <c r="E18" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0</v>
-      </c>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -849,12 +1137,26 @@
       <c r="D19" t="n">
         <v>4000</v>
       </c>
-      <c r="E19" t="n">
-        <v>151</v>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F19" t="n">
-        <v>65</v>
-      </c>
+        <v>138</v>
+      </c>
+      <c r="G19" t="n">
+        <v>46</v>
+      </c>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -871,12 +1173,18 @@
       <c r="D20" t="n">
         <v>908</v>
       </c>
-      <c r="E20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0</v>
-      </c>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -893,12 +1201,26 @@
       <c r="D21" t="n">
         <v>1208</v>
       </c>
-      <c r="E21" t="n">
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
         <v>163</v>
       </c>
-      <c r="F21" t="n">
+      <c r="G21" t="n">
         <v>44</v>
       </c>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -915,12 +1237,42 @@
       <c r="D22" t="n">
         <v>960</v>
       </c>
-      <c r="E22" t="n">
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
         <v>101</v>
       </c>
-      <c r="F22" t="n">
+      <c r="G22" t="n">
         <v>44</v>
       </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
+        <v>68</v>
+      </c>
+      <c r="J22" t="n">
+        <v>39</v>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="L22" t="n">
+        <v>71</v>
+      </c>
+      <c r="M22" t="n">
+        <v>19</v>
+      </c>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr"/>
+      <c r="P22" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
